--- a/Colorado/WaterAllocation/COwr_Allocation Schema Mapping to WaDE.xlsx
+++ b/Colorado/WaterAllocation/COwr_Allocation Schema Mapping to WaDE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rjame\Documents\WSWC Documents\MappingStatesDataToWaDE2.0\Colorado\WaterAllocation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B42C43-A274-4690-8145-24A50BDFF75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B49DEE-7F5A-42E3-A7E1-CD3B1B3E0533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2475" windowWidth="29040" windowHeight="15720" tabRatio="645" activeTab="2" xr2:uid="{00CC2BD5-2C7C-4716-9573-3E594BB9D2D1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="645" activeTab="1" xr2:uid="{00CC2BD5-2C7C-4716-9573-3E594BB9D2D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping Notes" sheetId="1" r:id="rId1"/>
@@ -897,9 +897,6 @@
     <t>https://drive.google.com/file/d/14r6HBwqebBwSE60yuiUu1smmtDONJbu2/view</t>
   </si>
   <si>
-    <t>https://github.com/WSWCWaterDataExchange/MappingStatesDataToWaDE2.0/tree/master/Colorado/WaterAllocation_WaterUse</t>
-  </si>
-  <si>
     <t>COwr_V1</t>
   </si>
   <si>
@@ -1036,6 +1033,9 @@
   </si>
   <si>
     <t>Annual</t>
+  </si>
+  <si>
+    <t>https://github.com/WSWCWaterDataExchange/MappingStatesDataToWaDE2.0/tree/master/Colorado/WaterAllocation</t>
   </si>
 </sst>
 </file>
@@ -1981,7 +1981,7 @@
         <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C2" s="48" t="s">
         <v>108</v>
@@ -1992,7 +1992,7 @@
         <v>109</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C3" s="48" t="s">
         <v>110</v>
@@ -2011,7 +2011,7 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C5" s="48"/>
     </row>
@@ -2476,7 +2476,7 @@
         <v>7</v>
       </c>
       <c r="F12" s="85" t="s">
-        <v>285</v>
+        <v>329</v>
       </c>
       <c r="G12" s="31" t="s">
         <v>7</v>
@@ -2611,7 +2611,7 @@
         <v>7</v>
       </c>
       <c r="F3" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G3" s="52" t="s">
         <v>7</v>
@@ -2681,7 +2681,7 @@
         <v>10</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G5" s="31" t="s">
         <v>7</v>
@@ -3064,7 +3064,7 @@
         <v>7</v>
       </c>
       <c r="F3" s="59" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G3" s="52" t="s">
         <v>7</v>
@@ -3099,7 +3099,7 @@
         <v>7</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G4" s="31" t="s">
         <v>7</v>
@@ -3134,7 +3134,7 @@
         <v>7</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G5" s="31" t="s">
         <v>7</v>
@@ -3169,7 +3169,7 @@
         <v>7</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G6" s="31" t="s">
         <v>7</v>
@@ -3204,7 +3204,7 @@
         <v>7</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G7" s="31" t="s">
         <v>7</v>
@@ -3239,7 +3239,7 @@
         <v>7</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G8" s="31" t="s">
         <v>7</v>
@@ -3274,7 +3274,7 @@
         <v>7</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G9" s="31" t="s">
         <v>7</v>
@@ -3309,7 +3309,7 @@
         <v>10</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G10" s="31" t="s">
         <v>7</v>
@@ -3471,7 +3471,7 @@
         <v>7</v>
       </c>
       <c r="F3" s="74" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G3" s="52"/>
       <c r="H3" s="62"/>
@@ -3603,13 +3603,13 @@
         <v>7</v>
       </c>
       <c r="F7" s="86" t="s">
+        <v>295</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="H7" s="55" t="s">
         <v>296</v>
-      </c>
-      <c r="G7" s="31" t="s">
-        <v>302</v>
-      </c>
-      <c r="H7" s="55" t="s">
-        <v>297</v>
       </c>
       <c r="I7" s="64" t="s">
         <v>7</v>
@@ -3638,13 +3638,13 @@
         <v>7</v>
       </c>
       <c r="F8" s="86" t="s">
+        <v>297</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="H8" s="55" t="s">
         <v>298</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>302</v>
-      </c>
-      <c r="H8" s="55" t="s">
-        <v>299</v>
       </c>
       <c r="I8" s="40" t="s">
         <v>7</v>
@@ -3673,13 +3673,13 @@
         <v>10</v>
       </c>
       <c r="F9" s="86" t="s">
+        <v>299</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="H9" s="55" t="s">
         <v>300</v>
-      </c>
-      <c r="G9" s="31" t="s">
-        <v>302</v>
-      </c>
-      <c r="H9" s="55" t="s">
-        <v>301</v>
       </c>
       <c r="I9" s="64" t="s">
         <v>7</v>
@@ -3824,7 +3824,7 @@
         <v>7</v>
       </c>
       <c r="F3" s="61" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G3" s="52"/>
       <c r="H3" s="53"/>
@@ -3855,7 +3855,7 @@
         <v>10</v>
       </c>
       <c r="F4" s="45" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G4" s="45" t="s">
         <v>7</v>
@@ -3888,7 +3888,7 @@
         <v>10</v>
       </c>
       <c r="F5" s="68" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G5" s="68"/>
       <c r="H5" s="69"/>
@@ -3955,10 +3955,10 @@
         <v>7</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H7" s="87" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I7" s="66" t="s">
         <v>7</v>
@@ -3988,7 +3988,7 @@
         <v>7</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H8" s="55" t="s">
         <v>36</v>
@@ -4188,7 +4188,7 @@
         <v>7</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H14" s="55" t="s">
         <v>91</v>
@@ -4223,7 +4223,7 @@
         <v>7</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H15" s="55" t="s">
         <v>92</v>
@@ -4359,10 +4359,10 @@
         <v>7</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H19" s="87" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I19" s="66" t="s">
         <v>7</v>
@@ -4394,10 +4394,10 @@
         <v>7</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H20" s="55" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I20" s="66" t="s">
         <v>7</v>
@@ -4459,13 +4459,13 @@
         <v>10</v>
       </c>
       <c r="F22" s="88" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H22" s="87" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I22" s="66" t="s">
         <v>7</v>
@@ -4494,7 +4494,7 @@
         <v>10</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G23" s="65" t="s">
         <v>7</v>
@@ -4791,7 +4791,7 @@
         <v>7</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F8" s="68"/>
       <c r="G8" s="69"/>
@@ -4845,7 +4845,7 @@
         <v>7</v>
       </c>
       <c r="E10" s="77" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F10" s="65" t="s">
         <v>7</v>
@@ -4877,7 +4877,7 @@
         <v>7</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F11" s="65" t="s">
         <v>7</v>
@@ -4909,7 +4909,7 @@
         <v>7</v>
       </c>
       <c r="E12" s="92" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F12" s="61" t="s">
         <v>7</v>
@@ -5136,7 +5136,7 @@
         <v>104</v>
       </c>
       <c r="F19" s="68" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G19" s="70" t="s">
         <v>7</v>
@@ -5197,13 +5197,13 @@
         <v>7</v>
       </c>
       <c r="E21" s="96" t="s">
+        <v>312</v>
+      </c>
+      <c r="F21" s="65" t="s">
+        <v>301</v>
+      </c>
+      <c r="G21" s="70" t="s">
         <v>313</v>
-      </c>
-      <c r="F21" s="65" t="s">
-        <v>302</v>
-      </c>
-      <c r="G21" s="70" t="s">
-        <v>314</v>
       </c>
       <c r="H21" s="13" t="s">
         <v>7</v>
@@ -5229,13 +5229,13 @@
         <v>10</v>
       </c>
       <c r="E22" s="96" t="s">
+        <v>314</v>
+      </c>
+      <c r="F22" s="65" t="s">
+        <v>301</v>
+      </c>
+      <c r="G22" s="70" t="s">
         <v>315</v>
-      </c>
-      <c r="F22" s="65" t="s">
-        <v>302</v>
-      </c>
-      <c r="G22" s="70" t="s">
-        <v>316</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>7</v>
@@ -5261,13 +5261,13 @@
         <v>7</v>
       </c>
       <c r="E23" s="96" t="s">
+        <v>316</v>
+      </c>
+      <c r="F23" s="65" t="s">
+        <v>301</v>
+      </c>
+      <c r="G23" s="70" t="s">
         <v>317</v>
-      </c>
-      <c r="F23" s="65" t="s">
-        <v>302</v>
-      </c>
-      <c r="G23" s="70" t="s">
-        <v>318</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>7</v>
@@ -5328,10 +5328,10 @@
         <v>7</v>
       </c>
       <c r="F25" s="65" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G25" s="70" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>7</v>
@@ -5357,7 +5357,7 @@
         <v>7</v>
       </c>
       <c r="E26" s="65" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F26" s="68" t="s">
         <v>7</v>
@@ -5389,7 +5389,7 @@
         <v>7</v>
       </c>
       <c r="E27" s="65" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F27" s="68" t="s">
         <v>7</v>
@@ -5453,13 +5453,13 @@
         <v>7</v>
       </c>
       <c r="E29" s="96" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F29" s="65" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G29" s="70" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H29" s="13" t="s">
         <v>7</v>
@@ -5471,7 +5471,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="24" x14ac:dyDescent="0.3">
       <c r="A30" s="42" t="s">
         <v>101</v>
       </c>
@@ -5485,13 +5485,13 @@
         <v>7</v>
       </c>
       <c r="E30" s="96" t="s">
+        <v>322</v>
+      </c>
+      <c r="F30" s="65" t="s">
+        <v>301</v>
+      </c>
+      <c r="G30" s="70" t="s">
         <v>323</v>
-      </c>
-      <c r="F30" s="65" t="s">
-        <v>302</v>
-      </c>
-      <c r="G30" s="70" t="s">
-        <v>324</v>
       </c>
       <c r="H30" s="13" t="s">
         <v>7</v>
@@ -5613,7 +5613,7 @@
         <v>7</v>
       </c>
       <c r="E34" s="65" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F34" s="68" t="s">
         <v>7</v>
@@ -6015,7 +6015,7 @@
         <v>7</v>
       </c>
       <c r="G46" s="70" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H46" s="13" t="s">
         <v>7</v>
